--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_DEER_ANTLERLESS.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_DEER_ANTLERLESS.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -535,6 +535,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -598,10 +599,15 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Average Harvest Age Prior Year</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>Avg Days Hunted Prior Year</t>
         </is>
@@ -661,7 +667,8 @@
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
@@ -721,7 +728,8 @@
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr"/>
-      <c r="N5" s="6" t="inlineStr">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" s="6" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
@@ -781,7 +789,8 @@
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
@@ -841,7 +850,8 @@
         </is>
       </c>
       <c r="M7" s="6" t="inlineStr"/>
-      <c r="N7" s="6" t="inlineStr">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" s="6" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
@@ -909,7 +919,8 @@
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr"/>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
@@ -977,7 +988,8 @@
         </is>
       </c>
       <c r="M9" s="6" t="inlineStr"/>
-      <c r="N9" s="6" t="inlineStr">
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" s="6" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
@@ -1045,7 +1057,8 @@
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr"/>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1105,7 +1118,8 @@
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr"/>
-      <c r="N11" s="6" t="inlineStr">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" s="6" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
@@ -1165,7 +1179,8 @@
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr"/>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
@@ -1225,7 +1240,8 @@
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr"/>
-      <c r="N13" s="6" t="inlineStr">
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" s="6" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -1285,7 +1301,8 @@
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr"/>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
@@ -1345,7 +1362,8 @@
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr"/>
-      <c r="N15" s="6" t="inlineStr">
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" s="6" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
@@ -1405,7 +1423,8 @@
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr"/>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
@@ -1465,7 +1484,8 @@
         </is>
       </c>
       <c r="M17" s="6" t="inlineStr"/>
-      <c r="N17" s="6" t="inlineStr">
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" s="6" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
@@ -1525,7 +1545,8 @@
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr"/>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -1585,7 +1606,8 @@
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr"/>
-      <c r="N19" s="6" t="inlineStr">
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" s="6" t="inlineStr">
         <is>
           <t>5.2</t>
         </is>
@@ -1645,7 +1667,8 @@
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr"/>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
@@ -1705,7 +1728,8 @@
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr"/>
-      <c r="N21" s="6" t="inlineStr">
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" s="6" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
@@ -1765,7 +1789,8 @@
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr"/>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" s="4" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
@@ -1833,7 +1858,8 @@
         </is>
       </c>
       <c r="M23" s="6" t="inlineStr"/>
-      <c r="N23" s="6" t="inlineStr">
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
